--- a/artfynd/A 51343-2024 artfynd.xlsx
+++ b/artfynd/A 51343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128296250</v>
       </c>
       <c r="B2" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51343-2024 artfynd.xlsx
+++ b/artfynd/A 51343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128296250</v>
       </c>
       <c r="B2" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51343-2024 artfynd.xlsx
+++ b/artfynd/A 51343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128296250</v>
       </c>
       <c r="B2" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51343-2024 artfynd.xlsx
+++ b/artfynd/A 51343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128296250</v>
       </c>
       <c r="B2" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51343-2024 artfynd.xlsx
+++ b/artfynd/A 51343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128296250</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51343-2024 artfynd.xlsx
+++ b/artfynd/A 51343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128296250</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51343-2024 artfynd.xlsx
+++ b/artfynd/A 51343-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128296250</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
